--- a/门诊排班模板.xlsx
+++ b/门诊排班模板.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18350" windowHeight="6880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="14055" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="号源排班" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -34,6 +34,13 @@
       <charset val="134"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="等线"/>
@@ -498,152 +505,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -657,13 +664,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -671,16 +675,9 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1280,19 +1277,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.8916666666667" customWidth="1" style="2" min="1" max="1"/>
     <col width="8.891666666666669" customWidth="1" style="2" min="2" max="2"/>
     <col width="19.8916666666667" customWidth="1" style="2" min="3" max="4"/>
-    <col width="20.4416666666667" customWidth="1" style="2" min="5" max="6"/>
-    <col width="13.1083333333333" customWidth="1" style="2" min="7" max="7"/>
-    <col width="14.4416666666667" customWidth="1" style="2" min="8" max="8"/>
-    <col width="20.775" customWidth="1" style="2" min="9" max="9"/>
-    <col width="21.4416666666667" customWidth="1" style="2" min="10" max="10"/>
-    <col width="8.891666666666669" customWidth="1" style="2" min="11" max="18"/>
-    <col width="9" customWidth="1" style="3" min="19" max="16384"/>
+    <col width="8.891666666666669" customWidth="1" style="2" min="5" max="5"/>
+    <col width="37.6666666666667" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13.1083333333333" customWidth="1" style="2" min="7" max="8"/>
+    <col width="14.4416666666667" customWidth="1" style="2" min="9" max="9"/>
+    <col width="20.775" customWidth="1" style="2" min="10" max="10"/>
+    <col width="21.4416666666667" customWidth="1" style="2" min="11" max="11"/>
+    <col width="15.4416666666667" customWidth="1" style="2" min="12" max="12"/>
+    <col width="14.6666666666667" customWidth="1" style="2" min="13" max="13"/>
+    <col width="8.891666666666669" customWidth="1" style="2" min="14" max="14"/>
+    <col width="9" customWidth="1" style="3" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -1328,32 +1328,44 @@
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
+          <t>业务科室名称</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
           <t>坐诊医生编码</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>号别名称</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>诊室名称</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>分诊台名称</t>
         </is>
       </c>
-      <c r="K1" s="10" t="n"/>
-      <c r="L1" s="10" t="n"/>
-      <c r="M1" s="10" t="n"/>
-      <c r="N1" s="10" t="n"/>
-      <c r="O1" s="10" t="n"/>
-      <c r="P1" s="10" t="n"/>
-      <c r="Q1" s="10" t="n"/>
-      <c r="R1" s="10" t="n"/>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>每个时间间隔号数</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>时间间隔（分钟）</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>现场号数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -1376,30 +1388,54 @@
           <t>2027-03-01 12:00:00</t>
         </is>
       </c>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>示例机构</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>示例科室</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
+          <t>示例业务科室</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
           <t>doctor001</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>医师</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>住院医师</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>示例诊室1</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>示例分诊台</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1424,30 +1460,54 @@
           <t>2027-03-01 17:30:00</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>示例机构</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>示例科室</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
+          <t>示例业务科室</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
           <t>doctor001</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>医师</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>住院医师</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>示例诊室1</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>示例分诊台</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1472,30 +1532,54 @@
           <t>2027-03-01 12:00:00</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>示例机构</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>示例科室</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
+          <t>示例业务科室</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>doctor002</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>示例诊室2</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>示例分诊台</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1520,30 +1604,54 @@
           <t>2027-03-01 17:30:00</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>示例机构</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>示例科室</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
+          <t>示例业务科室</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
           <t>doctor002</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>示例诊室2</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>示例分诊台</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1568,30 +1676,54 @@
           <t>2027-03-02 12:00:00</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>示例机构</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>示例科室</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
+          <t>示例业务科室</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>doctor003</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>示例诊室3</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>示例分诊台</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1616,34 +1748,57 @@
           <t>2027-03-02 17:30:00</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>示例机构</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>示例科室</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
+          <t>示例业务科室</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
           <t>doctor003</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>示例诊室3</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>示例分诊台</t>
         </is>
       </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
-    <row r="20" ht="13" customHeight="1" s="12"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
